--- a/Models/КРС/results/КРС - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/КРС/results/КРС - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>170.89</v>
+        <v>195.14</v>
       </c>
       <c r="C2" t="n">
-        <v>146.6</v>
+        <v>156.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.22</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>887.97</v>
+        <v>440.52</v>
       </c>
       <c r="C3" t="n">
-        <v>728.64</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>12.77</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>918.74</v>
+        <v>645.16</v>
       </c>
       <c r="C4" t="n">
-        <v>730.59</v>
+        <v>469.63</v>
       </c>
       <c r="D4" t="n">
-        <v>11.63</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>160.94</v>
+        <v>143.89</v>
       </c>
       <c r="C5" t="n">
-        <v>142.53</v>
+        <v>132.2</v>
       </c>
       <c r="D5" t="n">
-        <v>8.609999999999999</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>439.2</v>
+        <v>319.08</v>
       </c>
       <c r="C6" t="n">
-        <v>383.63</v>
+        <v>260.7</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.46</v>
+        <v>10.45</v>
       </c>
       <c r="C7" t="n">
-        <v>3.69</v>
+        <v>7.86</v>
       </c>
       <c r="D7" t="n">
-        <v>87.36</v>
+        <v>2.286066562543349e+22</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="C8" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="D8" t="n">
-        <v>26.88</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>204.56</v>
+        <v>252.34</v>
       </c>
       <c r="C9" t="n">
-        <v>135.17</v>
+        <v>178.6</v>
       </c>
       <c r="D9" t="n">
-        <v>28.85</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>415.41</v>
+        <v>712.59</v>
       </c>
       <c r="C10" t="n">
-        <v>360.33</v>
+        <v>521.48</v>
       </c>
       <c r="D10" t="n">
-        <v>9.24</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>238.56</v>
+        <v>243.21</v>
       </c>
       <c r="C11" t="n">
-        <v>206.83</v>
+        <v>194.85</v>
       </c>
       <c r="D11" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>320.61</v>
+        <v>169.02</v>
       </c>
       <c r="C12" t="n">
-        <v>271.46</v>
+        <v>150.64</v>
       </c>
       <c r="D12" t="n">
-        <v>8.470000000000001</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1175.1</v>
+        <v>434.12</v>
       </c>
       <c r="C13" t="n">
-        <v>833.88</v>
+        <v>350.9</v>
       </c>
       <c r="D13" t="n">
-        <v>18.38</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>127.21</v>
+        <v>295.1</v>
       </c>
       <c r="C14" t="n">
-        <v>96.94</v>
+        <v>220.04</v>
       </c>
       <c r="D14" t="n">
-        <v>5.56</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50.89</v>
+        <v>32.32</v>
       </c>
       <c r="C15" t="n">
-        <v>36.48</v>
+        <v>20.85</v>
       </c>
       <c r="D15" t="n">
-        <v>20.85</v>
+        <v>43.21</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1408.26</v>
+        <v>659.85</v>
       </c>
       <c r="C16" t="n">
-        <v>1301.98</v>
+        <v>548.97</v>
       </c>
       <c r="D16" t="n">
-        <v>50.75</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3278.45</v>
+        <v>1973.46</v>
       </c>
       <c r="C17" t="n">
-        <v>3022.62</v>
+        <v>1753.38</v>
       </c>
       <c r="D17" t="n">
-        <v>73.61</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>234.13</v>
+        <v>95.17</v>
       </c>
       <c r="C18" t="n">
-        <v>216.25</v>
+        <v>85.27</v>
       </c>
       <c r="D18" t="n">
-        <v>78.15000000000001</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>672.08</v>
+        <v>494.4</v>
       </c>
       <c r="C19" t="n">
-        <v>577.74</v>
+        <v>430.62</v>
       </c>
       <c r="D19" t="n">
-        <v>14.19</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>212.14</v>
+        <v>196.45</v>
       </c>
       <c r="C20" t="n">
-        <v>186.23</v>
+        <v>150.04</v>
       </c>
       <c r="D20" t="n">
-        <v>8.23</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4190.03</v>
+        <v>3630.81</v>
       </c>
       <c r="C21" t="n">
-        <v>2964.91</v>
+        <v>2473.98</v>
       </c>
       <c r="D21" t="n">
-        <v>22.88</v>
+        <v>16.74</v>
       </c>
     </row>
   </sheetData>
